--- a/docs/Requisitos_Não_Funcionais_Plataforma_UNIFEI.xlsx
+++ b/docs/Requisitos_Não_Funcionais_Plataforma_UNIFEI.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Requisitos Não-Funcionais" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requisitos Não-Funcionais'!$A$1:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requisitos Não-Funcionais'!$A$1:$G$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G50,"CRÍTICA")</f>
+        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G51,"CRÍTICA")</f>
         <v/>
       </c>
     </row>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G50,"ESSENCIAL")</f>
+        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G51,"ESSENCIAL")</f>
         <v/>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G50,"IMPORTANTE")</f>
+        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G51,"IMPORTANTE")</f>
         <v/>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G50,"DESEJÁVEL")</f>
+        <f>COUNTIF('Requisitos Não-Funcionais'!G2:G51,"DESEJÁVEL")</f>
         <v/>
       </c>
     </row>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTA('Requisitos Não-Funcionais'!B2:B50)</f>
+        <f>COUNTA('Requisitos Não-Funcionais'!B2:B51)</f>
         <v/>
       </c>
     </row>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>RNF-INT-004</t>
+          <t>RNF-INT-005</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Identificadores não sequenciais</t>
+          <t>Separação entre intenção e fato registrado</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1220,17 +1220,17 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>O identificador de um registro não revela quantos existem nem permite percorrer os vizinhos.</t>
+          <t>O que a pessoa declara e o que a organização confirma são guardados em campos distintos, e apenas o confirmado é contabilizado.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Chaves primárias em UUID em todos os modelos.</t>
+          <t>Na campanha de doação, quantidade declarada e quantidade confirmada coexistem. Somar a declaração exibiria uma arrecadação que nunca chegou; guardar só a confirmação apagaria o registro da intenção — e a diferença entre os dois números é, ela própria, um dado sobre a campanha.</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -1240,32 +1240,32 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>RNF-DES-001</t>
+          <t>RNF-INT-004</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Consulta sem multiplicação de acessos</t>
+          <t>Identificadores não sequenciais</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Desempenho</t>
+          <t>Integridade</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Listas com dados relacionados não disparam uma consulta por item.</t>
+          <t>O identificador de um registro não revela quantos existem nem permite percorrer os vizinhos.</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Uso de select_related e prefetch_related nas consultas que compõem listagens. O acervo de arquivos, que atravessa três modelos, foi montado com esse cuidado.</t>
+          <t>Chaves primárias em UUID em todos os modelos.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>RNF-DES-002</t>
+          <t>RNF-DES-001</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Índices nos campos de filtro e ordenação</t>
+          <t>Consulta sem multiplicação de acessos</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>As consultas frequentes têm suporte de índice.</t>
+          <t>Listas com dados relacionados não disparam uma consulta por item.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Índices declarados em conversa e data de mensagem, em tipo de conversa e em data de criação de publicação.</t>
+          <t>Uso de select_related e prefetch_related nas consultas que compõem listagens. O acervo de arquivos, que atravessa três modelos, foi montado com esse cuidado.</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>RNF-DES-003</t>
+          <t>RNF-DES-002</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Paginação nas listagens</t>
+          <t>Índices nos campos de filtro e ordenação</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Nenhuma listagem devolve a coleção inteira.</t>
+          <t>As consultas frequentes têm suporte de índice.</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Paginação padrão do DRF configurada globalmente.</t>
+          <t>Índices declarados em conversa e data de mensagem, em tipo de conversa e em data de criação de publicação.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>RNF-DES-004</t>
+          <t>RNF-DES-003</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Custo de rede evitado em listagem</t>
+          <t>Paginação nas listagens</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Montar uma lista não faz uma chamada ao armazenamento por item.</t>
+          <t>Nenhuma listagem devolve a coleção inteira.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>O acervo não consulta o tamanho de cada anexo de conversa, porque a mensagem não o guarda e perguntar ao arquivo custaria uma chamada de rede por linha quando o armazenamento é externo.</t>
+          <t>Paginação padrão do DRF configurada globalmente.</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>RNF-DES-005</t>
+          <t>RNF-DES-004</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Modelo de linguagem carregado sob demanda</t>
+          <t>Custo de rede evitado em listagem</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>O modelo de busca semântica não é carregado na partida da aplicação.</t>
+          <t>Montar uma lista não faz uma chamada ao armazenamento por item.</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Carregamento tardio, na primeira indexação. Em instância pequena, o carregamento na partida esgotaria a memória antes de a aplicação responder.</t>
+          <t>O acervo não consulta o tamanho de cada anexo de conversa, porque a mensagem não o guarda e perguntar ao arquivo custaria uma chamada de rede por linha quando o armazenamento é externo.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>RNF-DES-006</t>
+          <t>RNF-DES-005</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Latência do canal em tempo real</t>
+          <t>Modelo de linguagem carregado sob demanda</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1430,17 +1430,17 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>A mensagem enviada aparece para os demais sem demora perceptível.</t>
+          <t>O modelo de busca semântica não é carregado na partida da aplicação.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Entrega por WebSocket sobre Daphne, sem consulta periódica ao servidor. A consulta periódica geraria carga constante e ainda assim exibiria a mensagem com atraso.</t>
+          <t>Carregamento tardio, na primeira indexação. Em instância pequena, o carregamento na partida esgotaria a memória antes de a aplicação responder.</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>RNF-DES-007</t>
+          <t>RNF-DES-006</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Filtragem no navegador quando o volume permite</t>
+          <t>Latência do canal em tempo real</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>A busca dentro do acervo de arquivos responde a cada tecla, sem ida ao servidor.</t>
+          <t>A mensagem enviada aparece para os demais sem demora perceptível.</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>O acervo de um semestre são dezenas de arquivos, não milhares. Consultar o servidor a cada tecla custaria mais que filtrar o conjunto inteiro localmente.</t>
+          <t>Entrega por WebSocket sobre Daphne, sem consulta periódica ao servidor. A consulta periódica geraria carga constante e ainda assim exibiria a mensagem com atraso.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>RNF-CON-001</t>
+          <t>RNF-DES-007</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Degradação previsível da busca</t>
+          <t>Filtragem no navegador quando o volume permite</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Confiabilidade</t>
+          <t>Desempenho</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Sem o modelo semântico, a busca continua funcionando em modo textual.</t>
+          <t>A busca dentro do acervo de arquivos responde a cada tecla, sem ida ao servidor.</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>A função de busca devolve o modo utilizado junto com os resultados, e a troca é automática. A interface informa qual modo respondeu.</t>
+          <t>O acervo de um semestre são dezenas de arquivos, não milhares. Consultar o servidor a cada tecla custaria mais que filtrar o conjunto inteiro localmente.</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>RNF-CON-002</t>
+          <t>RNF-CON-001</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Operação sem Redis</t>
+          <t>Degradação previsível da busca</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>A plataforma funciona em implantação de instância única, sem serviço de fila externo.</t>
+          <t>Sem o modelo semântico, a busca continua funcionando em modo textual.</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Camada de canais em memória e cache local quando Redis está desativado por variável de ambiente. Torna viável a implantação em plano gratuito, usada na avaliação com usuários.</t>
+          <t>A função de busca devolve o modo utilizado junto com os resultados, e a troca é automática. A interface informa qual modo respondeu.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>RNF-CON-003</t>
+          <t>RNF-CON-002</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Falha de carga não impede o acesso</t>
+          <t>Operação sem Redis</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Um erro na carga inicial não derruba a aplicação, e aparece no registro.</t>
+          <t>A plataforma funciona em implantação de instância única, sem serviço de fila externo.</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Os passos da carga rodam em segundo plano, depois de o servidor abrir a porta, e cada falha é impressa em destaque. A versão anterior silenciava o erro: a plataforma subia vazia e o registro não dizia por quê.</t>
+          <t>Camada de canais em memória e cache local quando Redis está desativado por variável de ambiente. Torna viável a implantação em plano gratuito, usada na avaliação com usuários.</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>RNF-CON-004</t>
+          <t>RNF-CON-003</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Verificação automatizada</t>
+          <t>Falha de carga não impede o acesso</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>As regras de permissão e privacidade têm teste que as sustenta.</t>
+          <t>Um erro na carga inicial não derruba a aplicação, e aparece no registro.</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Suíte de testes automatizados cobrindo autenticação, visibilidade por matrícula, privacidade da conversa, moderação e o acervo de arquivos.</t>
+          <t>Os passos da carga rodam em segundo plano, depois de o servidor abrir a porta, e cada falha é impressa em destaque. A versão anterior silenciava o erro: a plataforma subia vazia e o registro não dizia por quê.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>RNF-CON-005</t>
+          <t>RNF-CON-004</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Reprodutibilidade do conjunto de demonstração</t>
+          <t>Verificação automatizada</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1640,17 +1640,17 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>A mesma carga produz sempre o mesmo conjunto de dados.</t>
+          <t>As regras de permissão e privacidade têm teste que as sustenta.</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Semente fixa no gerador aleatório do comando de demonstração. Sem isso, uma captura de tela do artigo não corresponderia ao que a banca veria ao executar o projeto.</t>
+          <t>Suíte de testes automatizados cobrindo autenticação, visibilidade por matrícula, privacidade da conversa, moderação e o acervo de arquivos.</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>RNF-CON-006</t>
+          <t>RNF-CON-005</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Carga inicial que não sobrescreve uso real</t>
+          <t>Reprodutibilidade do conjunto de demonstração</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1675,17 +1675,17 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>A carga de demonstração roda uma vez, e não a cada reinício.</t>
+          <t>A mesma carga produz sempre o mesmo conjunto de dados.</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Controlada por variável de ambiente, desligada após a primeira implantação. Repeti-la apagaria o que os participantes produziram durante a avaliação, que é justamente o dado a observar.</t>
+          <t>Semente fixa no gerador aleatório do comando de demonstração. Sem isso, uma captura de tela do artigo não corresponderia ao que a banca veria ao executar o projeto.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -1695,27 +1695,27 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>RNF-USA-001</t>
+          <t>RNF-CON-006</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Conformidade com diretrizes de acessibilidade</t>
+          <t>Carga inicial que não sobrescreve uso real</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Acessibilidade</t>
+          <t>Confiabilidade</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>A plataforma é utilizável por quem depende de leitor de tela ou navega por teclado.</t>
+          <t>A carga de demonstração roda uma vez, e não a cada reinício.</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Idioma declarado no elemento raiz, atalho para o conteúdo principal, contorno de foco visível, nome acessível em botões que só têm ícone, indicação da página atual na navegação e respeito à preferência de movimento reduzido. Segue as diretrizes da W3C.</t>
+          <t>Controlada por variável de ambiente, desligada após a primeira implantação. Repeti-la apagaria o que os participantes produziram durante a avaliação, que é justamente o dado a observar.</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>RNF-USA-002</t>
+          <t>RNF-USA-001</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Contraste suficiente nos dois temas</t>
+          <t>Conformidade com diretrizes de acessibilidade</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Texto e controles permanecem legíveis no tema claro e no escuro.</t>
+          <t>A plataforma é utilizável por quem depende de leitor de tela ou navega por teclado.</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Cores definidas por variáveis que trocam de valor com o tema. Valores fixos escritos no código produziam texto quase invisível no tema escuro.</t>
+          <t>Idioma declarado no elemento raiz, atalho para o conteúdo principal, contorno de foco visível, nome acessível em botões que só têm ícone, indicação da página atual na navegação e respeito à preferência de movimento reduzido. Segue as diretrizes da W3C.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -1765,27 +1765,27 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>RNF-USA-003</t>
+          <t>RNF-USA-002</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Adaptação a telas estreitas</t>
+          <t>Contraste suficiente nos dois temas</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Usabilidade</t>
+          <t>Acessibilidade</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>A plataforma é utilizável no telefone.</t>
+          <t>Texto e controles permanecem legíveis no tema claro e no escuro.</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Abaixo de 1024 pixels a barra lateral sai do fluxo e vira gaveta sobreposta. Grades de colunas fixas foram trocadas por ajuste automático, que só cria a segunda coluna quando há largura para ela. Campos com no mínimo 16 pixels, para o navegador não aproximar a página ao receber foco.</t>
+          <t>Cores definidas por variáveis que trocam de valor com o tema. Valores fixos escritos no código produziam texto quase invisível no tema escuro.</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>RNF-USA-004</t>
+          <t>RNF-USA-003</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Confirmação em ação de efeito coletivo</t>
+          <t>Adaptação a telas estreitas</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Sair de um grupo e excluir mensagem pedem confirmação.</t>
+          <t>A plataforma é utilizável no telefone.</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Diálogo antes de executar. São ações que afetam outras pessoas e cujo desfazer não é imediato.</t>
+          <t>Abaixo de 1024 pixels a barra lateral sai do fluxo e vira gaveta sobreposta. Grades de colunas fixas foram trocadas por ajuste automático, que só cria a segunda coluna quando há largura para ela. Campos com no mínimo 16 pixels, para o navegador não aproximar a página ao receber foco.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>RNF-USA-005</t>
+          <t>RNF-USA-004</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Mensagem de erro acionável</t>
+          <t>Confirmação em ação de efeito coletivo</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>O erro diz o que aconteceu e o que fazer.</t>
+          <t>Sair de um grupo e excluir mensagem pedem confirmação.</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>As recusas de regra de negócio devolvem texto explicativo em vez de código genérico. A migração da extensão vetorial distingue ausência de extensão de falta de permissão, e indica o comando a executar.</t>
+          <t>Diálogo antes de executar. São ações que afetam outras pessoas e cujo desfazer não é imediato.</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>RNF-USA-006</t>
+          <t>RNF-USA-005</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Estado vazio que orienta</t>
+          <t>Mensagem de erro acionável</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Tela sem conteúdo explica o que aparecerá ali e como fazer aparecer.</t>
+          <t>O erro diz o que aconteceu e o que fazer.</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Cada listagem tem texto próprio para o caso vazio, em vez de área em branco. Numa plataforma nova, o estado vazio é o mais frequente.</t>
+          <t>As recusas de regra de negócio devolvem texto explicativo em vez de código genérico. A migração da extensão vetorial distingue ausência de extensão de falta de permissão, e indica o comando a executar.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>RNF-USA-007</t>
+          <t>RNF-USA-006</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Contagem que não inventa número</t>
+          <t>Estado vazio que orienta</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Nenhum número exibido na interface é fixo no código.</t>
+          <t>Tela sem conteúdo explica o que aparecerá ali e como fazer aparecer.</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>As contagens da tela de entrada vêm de consulta real e mostram zero quando o valor é zero. Número inventado em tela institucional é problema de credibilidade: quem perguntar de onde vem não tem resposta.</t>
+          <t>Cada listagem tem texto próprio para o caso vazio, em vez de área em branco. Numa plataforma nova, o estado vazio é o mais frequente.</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>RNF-USA-008</t>
+          <t>RNF-USA-007</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Concordância de número no texto da interface</t>
+          <t>Contagem que não inventa número</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Singular e plural corretos em toda contagem exibida.</t>
+          <t>Nenhum número exibido na interface é fixo no código.</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Função utilitária de pluralização aplicada nas contagens. Detalhe pequeno, mas "1 oportunidades" desgasta a percepção de cuidado da plataforma inteira.</t>
+          <t>As contagens da tela de entrada vêm de consulta real e mostram zero quando o valor é zero. Número inventado em tela institucional é problema de credibilidade: quem perguntar de onde vem não tem resposta.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>DESEJÁVEL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -1975,32 +1975,32 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>RNF-MAN-001</t>
+          <t>RNF-USA-008</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Regras de negócio fora das views</t>
+          <t>Concordância de número no texto da interface</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Manutenibilidade</t>
+          <t>Usabilidade</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>A mesma regra vale para a API e para o canal em tempo real.</t>
+          <t>Singular e plural corretos em toda contagem exibida.</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>As regras vivem em módulos de serviço, usados tanto pelas views quanto pelo consumidor de WebSocket. Duplicá-las garantiria divergência.</t>
+          <t>Função utilitária de pluralização aplicada nas contagens. Detalhe pequeno, mas "1 oportunidades" desgasta a percepção de cuidado da plataforma inteira.</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>DESEJÁVEL</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>RNF-MAN-002</t>
+          <t>RNF-MAN-001</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Permissões centralizadas</t>
+          <t>Regras de negócio fora das views</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>A verificação de papel tem um único lugar de definição.</t>
+          <t>A mesma regra vale para a API e para o canal em tempo real.</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Módulo compartilhado em config/permissions, importado por todos os apps.</t>
+          <t>As regras vivem em módulos de serviço, usados tanto pelas views quanto pelo consumidor de WebSocket. Duplicá-las garantiria divergência.</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>RNF-MAN-003</t>
+          <t>RNF-MAN-002</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Documentação da API gerada do código</t>
+          <t>Permissões centralizadas</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2060,17 +2060,17 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>A especificação da API acompanha a implementação.</t>
+          <t>A verificação de papel tem um único lugar de definição.</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>drf-spectacular gera o esquema OpenAPI a partir das views e serializadores.</t>
+          <t>Módulo compartilhado em config/permissions, importado por todos os apps.</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>RNF-MAN-004</t>
+          <t>RNF-MAN-003</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Verificação de tipos antes da entrega</t>
+          <t>Documentação da API gerada do código</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2095,17 +2095,17 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Erro de tipo no frontend é detectado antes da implantação.</t>
+          <t>A especificação da API acompanha a implementação.</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>TypeScript com verificação na construção. O servidor de desenvolvimento não verifica tipos: oito erros sobreviveram uma semana e só apareceram na implantação.</t>
+          <t>drf-spectacular gera o esquema OpenAPI a partir das views e serializadores.</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2115,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>RNF-MAN-005</t>
+          <t>RNF-MAN-004</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Comentário que registra o motivo</t>
+          <t>Verificação de tipos antes da entrega</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2130,17 +2130,17 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>O código explica por que a decisão foi tomada, e não o que a linha faz.</t>
+          <t>Erro de tipo no frontend é detectado antes da implantação.</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Convenção adotada em todo o projeto. Reduz o risco de alguém desfazer uma correção por não conhecer o defeito que ela resolveu.</t>
+          <t>TypeScript com verificação na construção. O servidor de desenvolvimento não verifica tipos: oito erros sobreviveram uma semana e só apareceram na implantação.</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -2150,32 +2150,32 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>RNF-POR-001</t>
+          <t>RNF-MAN-005</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Implantação reprodutível em contêiner</t>
+          <t>Comentário que registra o motivo</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Portabilidade</t>
+          <t>Manutenibilidade</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>O ambiente de produção é construído sempre da mesma forma.</t>
+          <t>O código explica por que a decisão foi tomada, e não o que a linha faz.</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Dockerfile de duas etapas: uma constrói o frontend, outra executa a aplicação. Bibliotecas de sistema necessárias declaradas explicitamente.</t>
+          <t>Convenção adotada em todo o projeto. Reduz o risco de alguém desfazer uma correção por não conhecer o defeito que ela resolveu.</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>RNF-POR-002</t>
+          <t>RNF-POR-001</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Configuração por variável de ambiente</t>
+          <t>Implantação reprodutível em contêiner</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Nenhum segredo ou endereço fica escrito no código.</t>
+          <t>O ambiente de produção é construído sempre da mesma forma.</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Chave secreta, banco, hosts permitidos, armazenamento e chaves de serviços vêm do ambiente. Permite trocar de provedor sem alterar código.</t>
+          <t>Dockerfile de duas etapas: uma constrói o frontend, outra executa a aplicação. Bibliotecas de sistema necessárias declaradas explicitamente.</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>CRÍTICA</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>RNF-POR-003</t>
+          <t>RNF-POR-002</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Armazenamento de arquivos intercambiável</t>
+          <t>Configuração por variável de ambiente</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Os arquivos enviados podem ficar no disco local ou em serviço externo.</t>
+          <t>Nenhum segredo ou endereço fica escrito no código.</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Sistema de armazenamento escolhido por configuração, com django-storages. Necessário porque o disco do contêiner é efêmero.</t>
+          <t>Chave secreta, banco, hosts permitidos, armazenamento e chaves de serviços vêm do ambiente. Permite trocar de provedor sem alterar código.</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>CRÍTICA</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>RNF-POR-004</t>
+          <t>RNF-POR-003</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Entrega dos arquivos estáticos pela aplicação</t>
+          <t>Armazenamento de arquivos intercambiável</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>A aplicação serve o próprio frontend, sem servidor web separado.</t>
+          <t>Os arquivos enviados podem ficar no disco local ou em serviço externo.</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>WhiteNoise com compressão. O frontend é construído com prefixo de caminho compatível com o local de publicação — sem isso o navegador pede os arquivos no lugar errado e recebe a página em branco.</t>
+          <t>Sistema de armazenamento escolhido por configuração, com django-storages. Necessário porque o disco do contêiner é efêmero.</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>RNF-POR-005</t>
+          <t>RNF-POR-004</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Idioma declarado no documento</t>
+          <t>Entrega dos arquivos estáticos pela aplicação</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>O leitor de tela pronuncia o conteúdo em português.</t>
+          <t>A aplicação serve o próprio frontend, sem servidor web separado.</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Atributo de idioma no elemento raiz. Com o valor padrão do gerador, em inglês, palavras como "dúvida" e "matriculados" saem com fonética inglesa e a interface fica incompreensível para quem depende de áudio.</t>
+          <t>WhiteNoise com compressão. O frontend é construído com prefixo de caminho compatível com o local de publicação — sem isso o navegador pede os arquivos no lugar errado e recebe a página em branco.</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -2325,37 +2325,72 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
+          <t>RNF-POR-005</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Idioma declarado no documento</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Portabilidade</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>O leitor de tela pronuncia o conteúdo em português.</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Atributo de idioma no elemento raiz. Com o valor padrão do gerador, em inglês, palavras como "dúvida" e "matriculados" saem com fonética inglesa e a interface fica incompreensível para quem depende de áudio.</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>ESSENCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
           <t>RNF-POR-006</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Aplicação de página única servida pelo backend</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Portabilidade</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>Qualquer endereço da aplicação abre direto, sem passar pela raiz.</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Rota de captura no Django devolve a página principal para endereços que não sejam de API, administração ou arquivos. Sem ela, recarregar uma página interna resultaria em erro de página não encontrada.</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>ESSENCIAL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G50"/>
+  <autoFilter ref="A1:G51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>